--- a/docs/Sprint-2/product-backlog/Sprint Backlog.xlsx
+++ b/docs/Sprint-2/product-backlog/Sprint Backlog.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>Sprint Backlog</t>
   </si>
@@ -125,12 +125,6 @@
   </si>
   <si>
     <t>การเผยแพร่ระบบ</t>
-  </si>
-  <si>
-    <t>Test Data Preparation</t>
-  </si>
-  <si>
-    <t>รวบรวมรายชื่อสมมติของผู้โดยสาร เลขทะเบียน ที่ต้องใช้ในระบบ</t>
   </si>
   <si>
     <t>รวม</t>
@@ -316,7 +310,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="37">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -411,12 +405,6 @@
     <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
@@ -495,11 +483,11 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="556413672"/>
-        <c:axId val="400831749"/>
+        <c:axId val="1300051551"/>
+        <c:axId val="115942794"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="556413672"/>
+        <c:axId val="1300051551"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -551,10 +539,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="400831749"/>
+        <c:crossAx val="115942794"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="400831749"/>
+        <c:axId val="115942794"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -629,7 +617,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556413672"/>
+        <c:crossAx val="1300051551"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -1698,8 +1686,8 @@
       <c r="AD16" s="2"/>
     </row>
     <row r="17" ht="24.0" customHeight="1">
-      <c r="A17" s="22"/>
-      <c r="B17" s="22"/>
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
       <c r="C17" s="24" t="s">
         <v>36</v>
       </c>
@@ -1750,41 +1738,27 @@
       <c r="AC17" s="2"/>
       <c r="AD17" s="2"/>
     </row>
-    <row r="18" ht="58.5" customHeight="1">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="34" t="s">
+    <row r="18" ht="23.25" customHeight="1">
+      <c r="A18" s="34"/>
+      <c r="B18" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="35" t="s">
-        <v>39</v>
+      <c r="C18" s="8"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="34">
+        <f>SUM(E5:E17)</f>
+        <v>37</v>
       </c>
-      <c r="E18" s="20">
-        <v>2.0</v>
-      </c>
-      <c r="F18" s="31">
-        <v>2.0</v>
-      </c>
-      <c r="G18" s="31">
-        <v>2.0</v>
-      </c>
-      <c r="H18" s="31">
-        <v>0.0</v>
-      </c>
-      <c r="I18" s="31">
-        <v>0.0</v>
-      </c>
-      <c r="J18" s="31">
-        <v>0.0</v>
-      </c>
-      <c r="K18" s="31">
-        <v>0.0</v>
-      </c>
-      <c r="L18" s="31">
-        <v>0.0</v>
-      </c>
-      <c r="M18" s="20">
-        <v>2.0</v>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="34"/>
+      <c r="J18" s="34"/>
+      <c r="K18" s="34"/>
+      <c r="L18" s="34"/>
+      <c r="M18" s="34">
+        <f>SUM(M5:M17)</f>
+        <v>41</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
@@ -1803,28 +1777,20 @@
       <c r="AC18" s="2"/>
       <c r="AD18" s="2"/>
     </row>
-    <row r="19" ht="23.25" customHeight="1">
-      <c r="A19" s="36"/>
-      <c r="B19" s="37" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="36">
-        <f>SUM(E5:E18)</f>
-        <v>39</v>
-      </c>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="36"/>
-      <c r="I19" s="36"/>
-      <c r="J19" s="36"/>
-      <c r="K19" s="36"/>
-      <c r="L19" s="36"/>
-      <c r="M19" s="36">
-        <f>SUM(M5:M18)</f>
-        <v>43</v>
-      </c>
+    <row r="19" ht="14.25" customHeight="1">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
       <c r="Q19" s="2"/>
@@ -31017,7 +30983,7 @@
       <c r="A961" s="2"/>
       <c r="B961" s="2"/>
       <c r="C961" s="2"/>
-      <c r="D961" s="2"/>
+      <c r="D961" s="36"/>
       <c r="E961" s="2"/>
       <c r="F961" s="2"/>
       <c r="G961" s="2"/>
@@ -31048,7 +31014,7 @@
       <c r="A962" s="2"/>
       <c r="B962" s="2"/>
       <c r="C962" s="2"/>
-      <c r="D962" s="38"/>
+      <c r="D962" s="36"/>
       <c r="E962" s="2"/>
       <c r="F962" s="2"/>
       <c r="G962" s="2"/>
@@ -31078,16 +31044,16 @@
     <row r="963" ht="14.25" customHeight="1">
       <c r="A963" s="2"/>
       <c r="B963" s="2"/>
-      <c r="C963" s="2"/>
-      <c r="D963" s="38"/>
-      <c r="E963" s="2"/>
-      <c r="F963" s="2"/>
-      <c r="G963" s="2"/>
-      <c r="H963" s="2"/>
-      <c r="I963" s="2"/>
-      <c r="J963" s="2"/>
-      <c r="K963" s="2"/>
-      <c r="L963" s="2"/>
+      <c r="C963" s="36"/>
+      <c r="D963" s="36"/>
+      <c r="E963" s="36"/>
+      <c r="F963" s="36"/>
+      <c r="G963" s="36"/>
+      <c r="H963" s="36"/>
+      <c r="I963" s="36"/>
+      <c r="J963" s="36"/>
+      <c r="K963" s="36"/>
+      <c r="L963" s="36"/>
       <c r="M963" s="2"/>
       <c r="O963" s="2"/>
       <c r="P963" s="2"/>
@@ -31109,16 +31075,16 @@
     <row r="964" ht="14.25" customHeight="1">
       <c r="A964" s="2"/>
       <c r="B964" s="2"/>
-      <c r="C964" s="38"/>
-      <c r="D964" s="38"/>
-      <c r="E964" s="38"/>
-      <c r="F964" s="38"/>
-      <c r="G964" s="38"/>
-      <c r="H964" s="38"/>
-      <c r="I964" s="38"/>
-      <c r="J964" s="38"/>
-      <c r="K964" s="38"/>
-      <c r="L964" s="38"/>
+      <c r="C964" s="36"/>
+      <c r="D964" s="36"/>
+      <c r="E964" s="36"/>
+      <c r="F964" s="36"/>
+      <c r="G964" s="36"/>
+      <c r="H964" s="36"/>
+      <c r="I964" s="36"/>
+      <c r="J964" s="36"/>
+      <c r="K964" s="36"/>
+      <c r="L964" s="36"/>
       <c r="M964" s="2"/>
       <c r="O964" s="2"/>
       <c r="P964" s="2"/>
@@ -31137,37 +31103,6 @@
       <c r="AC964" s="2"/>
       <c r="AD964" s="2"/>
     </row>
-    <row r="965" ht="14.25" customHeight="1">
-      <c r="A965" s="2"/>
-      <c r="B965" s="2"/>
-      <c r="C965" s="38"/>
-      <c r="D965" s="38"/>
-      <c r="E965" s="38"/>
-      <c r="F965" s="38"/>
-      <c r="G965" s="38"/>
-      <c r="H965" s="38"/>
-      <c r="I965" s="38"/>
-      <c r="J965" s="38"/>
-      <c r="K965" s="38"/>
-      <c r="L965" s="38"/>
-      <c r="M965" s="2"/>
-      <c r="O965" s="2"/>
-      <c r="P965" s="2"/>
-      <c r="Q965" s="2"/>
-      <c r="R965" s="2"/>
-      <c r="S965" s="2"/>
-      <c r="T965" s="2"/>
-      <c r="U965" s="2"/>
-      <c r="V965" s="2"/>
-      <c r="W965" s="2"/>
-      <c r="X965" s="2"/>
-      <c r="Y965" s="2"/>
-      <c r="Z965" s="2"/>
-      <c r="AA965" s="2"/>
-      <c r="AB965" s="2"/>
-      <c r="AC965" s="2"/>
-      <c r="AD965" s="2"/>
-    </row>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="E4:E5"/>
@@ -31175,16 +31110,16 @@
     <mergeCell ref="P5:R5"/>
     <mergeCell ref="Y5:AD5"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A18"/>
-    <mergeCell ref="B6:B18"/>
-    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="A6:A17"/>
+    <mergeCell ref="B6:B17"/>
     <mergeCell ref="A1:M1"/>
-    <mergeCell ref="N1:N965"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="M4:M5"/>
+    <mergeCell ref="N1:N964"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
